--- a/Таблица сигналов.xlsx
+++ b/Таблица сигналов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DB\Projects\SW004-PalletWizardEco\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED98A765-BED8-4667-BBC1-92346D9F8093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140434CC-F8EB-4B77-A82E-9384433B740D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{FF0B67EC-BC3A-4258-B760-4C7AAB2595E4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF0B67EC-BC3A-4258-B760-4C7AAB2595E4}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>Комментарий</t>
   </si>
@@ -153,33 +153,6 @@
   </si>
   <si>
     <t>(Пусто)</t>
-  </si>
-  <si>
-    <t>Робот в домашнем положении</t>
-  </si>
-  <si>
-    <t>Переход на страницу 1 IF-панели</t>
-  </si>
-  <si>
-    <t>Переход на страницу 2 IF-панели</t>
-  </si>
-  <si>
-    <t>Переход на страницу 3 IF-панели</t>
-  </si>
-  <si>
-    <t>Переход на страницу 4 IF-панели</t>
-  </si>
-  <si>
-    <t>Переход на страницу 5 IF-панели</t>
-  </si>
-  <si>
-    <t>Переход на страницу 6 IF-панели</t>
-  </si>
-  <si>
-    <t>Переход на страницу 7 IF-панели</t>
-  </si>
-  <si>
-    <t>Переход на страницу 8 IF-панели</t>
   </si>
 </sst>
 </file>
@@ -222,17 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -285,18 +248,6 @@
     <tableColumn id="1" xr3:uid="{03419BA4-2836-4F5C-92E6-7B9CB498413D}" name="№"/>
     <tableColumn id="2" xr3:uid="{89D85D1E-780E-4D59-B471-D8C0E6558105}" name="Переменная"/>
     <tableColumn id="3" xr3:uid="{998BF2E9-FB14-4B86-A272-AE8D03A29828}" name="Комментарий"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E82A54F7-0E89-4B6A-97D8-3BCF9492EB48}" name="Таблица3" displayName="Таблица3" ref="I1:K45" totalsRowShown="0">
-  <autoFilter ref="I1:K45" xr:uid="{E82A54F7-0E89-4B6A-97D8-3BCF9492EB48}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E050D274-30DD-48E6-BA3D-287C1EDBABD9}" name="№"/>
-    <tableColumn id="2" xr3:uid="{E694DDF7-C54F-40B5-91E0-D7ADC9909E9F}" name="Переменная"/>
-    <tableColumn id="3" xr3:uid="{0AEDDB64-94D0-4CB8-B7A7-819163EDCCEC}" name="Комментарий"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -619,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{755FB8CD-7D75-4C2F-BCEC-A6D269DDC6B7}">
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
@@ -628,12 +579,9 @@
     <col min="5" max="5" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="51" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="33.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -652,17 +600,8 @@
       <c r="G1" t="s">
         <v>0</v>
       </c>
-      <c r="I1" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -675,14 +614,8 @@
       <c r="G2" t="s">
         <v>11</v>
       </c>
-      <c r="I2">
-        <v>2001</v>
-      </c>
-      <c r="K2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -695,14 +628,8 @@
       <c r="G3" t="s">
         <v>12</v>
       </c>
-      <c r="I3">
-        <v>2002</v>
-      </c>
-      <c r="K3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -715,14 +642,8 @@
       <c r="G4" t="s">
         <v>13</v>
       </c>
-      <c r="I4">
-        <v>2003</v>
-      </c>
-      <c r="K4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -732,14 +653,8 @@
       <c r="G5" t="s">
         <v>14</v>
       </c>
-      <c r="I5">
-        <v>2004</v>
-      </c>
-      <c r="K5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -749,14 +664,8 @@
       <c r="G6" t="s">
         <v>15</v>
       </c>
-      <c r="I6">
-        <v>2005</v>
-      </c>
-      <c r="K6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -766,14 +675,8 @@
       <c r="G7" t="s">
         <v>16</v>
       </c>
-      <c r="I7">
-        <v>2006</v>
-      </c>
-      <c r="K7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -783,14 +686,8 @@
       <c r="G8" t="s">
         <v>17</v>
       </c>
-      <c r="I8">
-        <v>2007</v>
-      </c>
-      <c r="K8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -800,39 +697,24 @@
       <c r="G9" t="s">
         <v>18</v>
       </c>
-      <c r="I9">
-        <v>2008</v>
-      </c>
-      <c r="K9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="E10">
         <v>1009</v>
       </c>
-      <c r="I10">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="E11">
         <v>1010</v>
       </c>
-      <c r="I11">
-        <v>2010</v>
-      </c>
-      <c r="K11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -842,11 +724,8 @@
       <c r="G12" t="s">
         <v>25</v>
       </c>
-      <c r="I12">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -856,198 +735,144 @@
       <c r="G13" t="s">
         <v>26</v>
       </c>
-      <c r="I13">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="E14">
         <v>1013</v>
       </c>
-      <c r="I14">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="E15">
         <v>1014</v>
       </c>
-      <c r="I15">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="E16">
         <v>1015</v>
       </c>
-      <c r="I16">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="E17">
         <v>1016</v>
       </c>
-      <c r="I17">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="E18">
         <v>1017</v>
       </c>
-      <c r="I18">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="E19">
         <v>1018</v>
       </c>
-      <c r="I19">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="E20">
         <v>1019</v>
       </c>
-      <c r="I20">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="E21">
         <v>1020</v>
       </c>
-      <c r="I21">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="E22">
         <v>1021</v>
       </c>
-      <c r="I22">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="E23">
         <v>1022</v>
       </c>
-      <c r="I23">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="E24">
         <v>1023</v>
       </c>
-      <c r="I24">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="E25">
         <v>1024</v>
       </c>
-      <c r="I25">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="E26">
         <v>1025</v>
       </c>
-      <c r="I26">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="E27">
         <v>1026</v>
       </c>
-      <c r="I27">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="E28">
         <v>1027</v>
       </c>
-      <c r="I28">
-        <v>2027</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="E29">
         <v>1028</v>
       </c>
-      <c r="I29">
-        <v>2028</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="E30">
         <v>1029</v>
       </c>
-      <c r="I30">
-        <v>2029</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1060,11 +885,8 @@
       <c r="G31" t="s">
         <v>21</v>
       </c>
-      <c r="I31">
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1077,11 +899,8 @@
       <c r="G32" t="s">
         <v>20</v>
       </c>
-      <c r="I32">
-        <v>2031</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1094,11 +913,8 @@
       <c r="G33" t="s">
         <v>19</v>
       </c>
-      <c r="I33">
-        <v>2032</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1111,11 +927,8 @@
       <c r="G34" t="s">
         <v>27</v>
       </c>
-      <c r="I34">
-        <v>2033</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1128,11 +941,8 @@
       <c r="G35" t="s">
         <v>28</v>
       </c>
-      <c r="I35">
-        <v>2034</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1145,11 +955,8 @@
       <c r="G36" t="s">
         <v>29</v>
       </c>
-      <c r="I36">
-        <v>2035</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1162,11 +969,8 @@
       <c r="G37" t="s">
         <v>30</v>
       </c>
-      <c r="I37">
-        <v>2036</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1179,11 +983,8 @@
       <c r="G38" t="s">
         <v>31</v>
       </c>
-      <c r="I38">
-        <v>2037</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1196,11 +997,8 @@
       <c r="G39" t="s">
         <v>32</v>
       </c>
-      <c r="I39">
-        <v>2038</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1210,11 +1008,8 @@
       <c r="G40" t="s">
         <v>33</v>
       </c>
-      <c r="I40">
-        <v>2039</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1224,11 +1019,8 @@
       <c r="G41" t="s">
         <v>34</v>
       </c>
-      <c r="I41">
-        <v>2040</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1238,11 +1030,8 @@
       <c r="G42" t="s">
         <v>35</v>
       </c>
-      <c r="I42">
-        <v>2041</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1252,11 +1041,8 @@
       <c r="G43" t="s">
         <v>36</v>
       </c>
-      <c r="I43">
-        <v>2042</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1266,42 +1052,30 @@
       <c r="G44" t="s">
         <v>37</v>
       </c>
-      <c r="I44">
-        <v>2043</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="E45">
         <v>1044</v>
       </c>
-      <c r="I45">
-        <v>2044</v>
-      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
       <formula>"ДЛИНА($B$2)&gt;15"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>"ДЛИНА($B$2)&gt;15"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>"ДЛИНА($B$2)&gt;15"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="3">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>